--- a/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Madhya Pradesh/results/SoIB_summaries.xlsx
@@ -529,7 +529,7 @@
         <v>50</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -540,13 +540,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C8">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,7 +750,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -761,10 +761,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>69.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>75.5</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>30.2</v>
+        <v>29.9</v>
       </c>
       <c r="D3">
         <v>24</v>
       </c>
       <c r="E3">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
     </row>
   </sheetData>
